--- a/research/traditional_assets/database/data/ghana/ghana_insurance_prop_cas.xlsx
+++ b/research/traditional_assets/database/data/ghana/ghana_insurance_prop_cas.xlsx
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.09</v>
+        <v>0.136</v>
       </c>
       <c r="E2">
-        <v>0.156</v>
+        <v>0.57</v>
       </c>
       <c r="G2">
-        <v>0.2171821305841924</v>
+        <v>0.3946428571428572</v>
       </c>
       <c r="H2">
-        <v>0.2171821305841924</v>
+        <v>0.3946428571428572</v>
       </c>
       <c r="I2">
-        <v>0.1735395189003436</v>
+        <v>0.1772321428571429</v>
       </c>
       <c r="J2">
-        <v>0.0915292821204344</v>
+        <v>0.1465148512646954</v>
       </c>
       <c r="K2">
-        <v>2.13</v>
+        <v>6.58</v>
       </c>
       <c r="L2">
-        <v>0.07319587628865978</v>
+        <v>0.29375</v>
       </c>
       <c r="M2">
-        <v>0.5868</v>
+        <v>0.978</v>
       </c>
       <c r="N2">
-        <v>0.2310236220472441</v>
+        <v>0.1572347266881029</v>
       </c>
       <c r="O2">
-        <v>0.2754929577464789</v>
+        <v>0.1486322188449848</v>
       </c>
       <c r="P2">
-        <v>0.5868</v>
+        <v>0.978</v>
       </c>
       <c r="Q2">
-        <v>0.2310236220472441</v>
+        <v>0.1572347266881029</v>
       </c>
       <c r="R2">
-        <v>0.2754929577464789</v>
+        <v>0.1486322188449848</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -642,10 +642,10 @@
         <v>0</v>
       </c>
       <c r="X2">
-        <v>0.1004891361401464</v>
+        <v>0.2232528321175561</v>
       </c>
       <c r="AB2">
-        <v>0.1004891361401464</v>
+        <v>0.2232528321175561</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -666,22 +666,22 @@
         <v>0</v>
       </c>
       <c r="AL2">
-        <v>0.333</v>
+        <v>0.294</v>
       </c>
       <c r="AM2">
-        <v>0.333</v>
+        <v>0.294</v>
       </c>
       <c r="AN2">
         <v>0</v>
       </c>
       <c r="AO2">
-        <v>15.16516516516516</v>
+        <v>13.50340136054422</v>
       </c>
       <c r="AP2">
         <v>0</v>
       </c>
       <c r="AQ2">
-        <v>15.16516516516516</v>
+        <v>13.50340136054422</v>
       </c>
     </row>
     <row r="3">
@@ -692,7 +692,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SIC Insurance Public Limited Company (PLC) (GHSE:SIC)</t>
+          <t>SIC Insurance PLC (GHSE:SIC)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -701,46 +701,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.09</v>
+        <v>0.136</v>
       </c>
       <c r="E3">
-        <v>0.156</v>
+        <v>0.57</v>
       </c>
       <c r="G3">
-        <v>0.2171821305841924</v>
+        <v>0.3946428571428572</v>
       </c>
       <c r="H3">
-        <v>0.2171821305841924</v>
+        <v>0.3946428571428572</v>
       </c>
       <c r="I3">
-        <v>0.1735395189003436</v>
+        <v>0.1772321428571429</v>
       </c>
       <c r="J3">
-        <v>0.0915292821204344</v>
+        <v>0.1465148512646954</v>
       </c>
       <c r="K3">
-        <v>2.13</v>
+        <v>6.58</v>
       </c>
       <c r="L3">
-        <v>0.07319587628865978</v>
+        <v>0.29375</v>
       </c>
       <c r="M3">
-        <v>0.5868</v>
+        <v>0.978</v>
       </c>
       <c r="N3">
-        <v>0.2310236220472441</v>
+        <v>0.1572347266881029</v>
       </c>
       <c r="O3">
-        <v>0.2754929577464789</v>
+        <v>0.1486322188449848</v>
       </c>
       <c r="P3">
-        <v>0.5868</v>
+        <v>0.978</v>
       </c>
       <c r="Q3">
-        <v>0.2310236220472441</v>
+        <v>0.1572347266881029</v>
       </c>
       <c r="R3">
-        <v>0.2754929577464789</v>
+        <v>0.1486322188449848</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -755,10 +755,10 @@
         <v>0</v>
       </c>
       <c r="X3">
-        <v>0.1004891361401464</v>
+        <v>0.2232528321175561</v>
       </c>
       <c r="AB3">
-        <v>0.1004891361401464</v>
+        <v>0.2232528321175561</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -779,22 +779,22 @@
         <v>0</v>
       </c>
       <c r="AL3">
-        <v>0.333</v>
+        <v>0.294</v>
       </c>
       <c r="AM3">
-        <v>0.333</v>
+        <v>0.294</v>
       </c>
       <c r="AN3">
         <v>0</v>
       </c>
       <c r="AO3">
-        <v>15.16516516516516</v>
+        <v>13.50340136054422</v>
       </c>
       <c r="AP3">
         <v>0</v>
       </c>
       <c r="AQ3">
-        <v>15.16516516516516</v>
+        <v>13.50340136054422</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/ghana/ghana_insurance_prop_cas.xlsx
+++ b/research/traditional_assets/database/data/ghana/ghana_insurance_prop_cas.xlsx
@@ -588,100 +588,115 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.136</v>
-      </c>
-      <c r="E2">
-        <v>0.57</v>
+        <v>0.108</v>
       </c>
       <c r="G2">
-        <v>0.3946428571428572</v>
+        <v>-0.05121052631578947</v>
       </c>
       <c r="H2">
-        <v>0.3946428571428572</v>
+        <v>-0.05121052631578947</v>
       </c>
       <c r="I2">
-        <v>0.1772321428571429</v>
+        <v>-0.1178947368421053</v>
       </c>
       <c r="J2">
-        <v>0.1465148512646954</v>
+        <v>-0.0798488529014845</v>
       </c>
       <c r="K2">
-        <v>6.58</v>
+        <v>1.81</v>
       </c>
       <c r="L2">
-        <v>0.29375</v>
+        <v>0.09526315789473684</v>
       </c>
       <c r="M2">
-        <v>0.978</v>
+        <v>0</v>
       </c>
       <c r="N2">
-        <v>0.1572347266881029</v>
+        <v>0</v>
       </c>
       <c r="O2">
-        <v>0.1486322188449848</v>
+        <v>0</v>
       </c>
       <c r="P2">
-        <v>0.978</v>
+        <v>0</v>
       </c>
       <c r="Q2">
-        <v>0.1572347266881029</v>
+        <v>0</v>
       </c>
       <c r="R2">
-        <v>0.1486322188449848</v>
+        <v>0</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
-      <c r="T2">
-        <v>0</v>
-      </c>
       <c r="U2">
-        <v>0</v>
+        <v>26.2</v>
       </c>
       <c r="V2">
-        <v>0</v>
+        <v>6.666666666666666</v>
+      </c>
+      <c r="W2">
+        <v>0.03716632443531828</v>
       </c>
       <c r="X2">
-        <v>0.2232528321175561</v>
+        <v>0.2028417868912463</v>
+      </c>
+      <c r="Y2">
+        <v>-0.165675462455928</v>
+      </c>
+      <c r="Z2">
+        <v>0.3515914137675795</v>
+      </c>
+      <c r="AA2">
+        <v>-0.02807417107935243</v>
       </c>
       <c r="AB2">
-        <v>0.2232528321175561</v>
+        <v>0.1801511935500104</v>
+      </c>
+      <c r="AC2">
+        <v>-0.2082253646293628</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG2">
-        <v>0</v>
+        <v>-24.67</v>
       </c>
       <c r="AH2">
-        <v>0</v>
+        <v>0.2802197802197802</v>
+      </c>
+      <c r="AI2">
+        <v>0.03666427030913012</v>
       </c>
       <c r="AJ2">
-        <v>0</v>
+        <v>1.189488910318226</v>
+      </c>
+      <c r="AK2">
+        <v>-1.588538312942691</v>
       </c>
       <c r="AL2">
-        <v>0.294</v>
+        <v>0.326</v>
       </c>
       <c r="AM2">
-        <v>0.294</v>
+        <v>0.326</v>
       </c>
       <c r="AN2">
-        <v>0</v>
+        <v>-1.57245632065776</v>
       </c>
       <c r="AO2">
-        <v>13.50340136054422</v>
+        <v>-6.871165644171779</v>
       </c>
       <c r="AP2">
-        <v>0</v>
+        <v>25.35457348406988</v>
       </c>
       <c r="AQ2">
-        <v>13.50340136054422</v>
+        <v>-6.871165644171779</v>
       </c>
     </row>
     <row r="3">
@@ -701,100 +716,115 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.136</v>
-      </c>
-      <c r="E3">
-        <v>0.57</v>
+        <v>0.108</v>
       </c>
       <c r="G3">
-        <v>0.3946428571428572</v>
+        <v>-0.05121052631578947</v>
       </c>
       <c r="H3">
-        <v>0.3946428571428572</v>
+        <v>-0.05121052631578947</v>
       </c>
       <c r="I3">
-        <v>0.1772321428571429</v>
+        <v>-0.1178947368421053</v>
       </c>
       <c r="J3">
-        <v>0.1465148512646954</v>
+        <v>-0.0798488529014845</v>
       </c>
       <c r="K3">
-        <v>6.58</v>
+        <v>1.81</v>
       </c>
       <c r="L3">
-        <v>0.29375</v>
+        <v>0.09526315789473684</v>
       </c>
       <c r="M3">
-        <v>0.978</v>
+        <v>-0</v>
       </c>
       <c r="N3">
-        <v>0.1572347266881029</v>
+        <v>-0</v>
       </c>
       <c r="O3">
-        <v>0.1486322188449848</v>
+        <v>-0</v>
       </c>
       <c r="P3">
-        <v>0.978</v>
+        <v>-0</v>
       </c>
       <c r="Q3">
-        <v>0.1572347266881029</v>
+        <v>-0</v>
       </c>
       <c r="R3">
-        <v>0.1486322188449848</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
       <c r="U3">
-        <v>0</v>
+        <v>26.2</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>6.666666666666666</v>
+      </c>
+      <c r="W3">
+        <v>0.03716632443531828</v>
       </c>
       <c r="X3">
-        <v>0.2232528321175561</v>
+        <v>0.2028417868912463</v>
+      </c>
+      <c r="Y3">
+        <v>-0.165675462455928</v>
+      </c>
+      <c r="Z3">
+        <v>0.3515914137675795</v>
+      </c>
+      <c r="AA3">
+        <v>-0.02807417107935243</v>
       </c>
       <c r="AB3">
-        <v>0.2232528321175561</v>
+        <v>0.1801511935500104</v>
+      </c>
+      <c r="AC3">
+        <v>-0.2082253646293628</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG3">
-        <v>0</v>
+        <v>-24.67</v>
       </c>
       <c r="AH3">
-        <v>0</v>
+        <v>0.2802197802197802</v>
+      </c>
+      <c r="AI3">
+        <v>0.03666427030913012</v>
       </c>
       <c r="AJ3">
-        <v>0</v>
+        <v>1.189488910318226</v>
+      </c>
+      <c r="AK3">
+        <v>-1.588538312942691</v>
       </c>
       <c r="AL3">
-        <v>0.294</v>
+        <v>0.326</v>
       </c>
       <c r="AM3">
-        <v>0.294</v>
+        <v>0.326</v>
       </c>
       <c r="AN3">
-        <v>0</v>
+        <v>-1.57245632065776</v>
       </c>
       <c r="AO3">
-        <v>13.50340136054422</v>
+        <v>-6.871165644171779</v>
       </c>
       <c r="AP3">
-        <v>0</v>
+        <v>25.35457348406988</v>
       </c>
       <c r="AQ3">
-        <v>13.50340136054422</v>
+        <v>-6.871165644171779</v>
       </c>
     </row>
   </sheetData>
